--- a/public/exports-from-60-with-coowners/29189625.xlsx
+++ b/public/exports-from-60-with-coowners/29189625.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258043</t>
+          <t xml:space="preserve">311258047</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286988</t>
+          <t xml:space="preserve">311286996</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -30664,7 +30664,7 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286960</t>
+          <t xml:space="preserve">311286964</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189625.xlsx
+++ b/public/exports-from-60-with-coowners/29189625.xlsx
@@ -17839,7 +17839,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265936</t>
+          <t xml:space="preserve">311265937</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286963</t>
+          <t xml:space="preserve">311286967</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -30739,7 +30739,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286990</t>
+          <t xml:space="preserve">311287000</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189625.xlsx
+++ b/public/exports-from-60-with-coowners/29189625.xlsx
@@ -14914,7 +14914,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258047</t>
+          <t xml:space="preserve">311258043</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265937</t>
+          <t xml:space="preserve">311265936</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286967</t>
+          <t xml:space="preserve">311286963</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286996</t>
+          <t xml:space="preserve">311286988</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -30664,7 +30664,7 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286964</t>
+          <t xml:space="preserve">311286960</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -30739,7 +30739,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287000</t>
+          <t xml:space="preserve">311286990</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
